--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="132" windowWidth="19392" windowHeight="7068"/>
+    <workbookView xWindow="600" yWindow="135" windowWidth="19395" windowHeight="7065"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="758">
+  <si>
+    <t>发起机构代码</t>
+  </si>
   <si>
     <t>产品种类</t>
   </si>
@@ -275,11 +278,118 @@
     <t>青海省</t>
   </si>
   <si>
+    <t>宁夏</t>
+  </si>
+  <si>
     <t>新疆维吾尔自治区</t>
   </si>
   <si>
     <t>${buyplace4000000.itemValue}</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>募集资金币种、兑付本金币种、兑付收益币种、客户类型、增信机构类型、增信形式如果有多个选项，使用&amp;分隔；
+起始募集信息，客户类型和募集币种，根据基本信息中的信息自行选择，将不需要的删除掉，需要增加的按照样式增加；
+数据填写使用中文名称；
+一个excel文件只能导入一只产品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">样式：文本
+选项：理财产品、资金信托计划 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">样式：文本
+</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：公募、私募</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：单独管理、集合管理</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：开放式净值型、开放式非净值型、封闭式净值型、封闭式非净值型</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：固定收益类、权益类、商品及金融衍生品类、混合类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：表内存款、表内非存款负债、表外</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：是、否</t>
+  </si>
+  <si>
+    <t>日期格式：YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>选项：有、无</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：有、无</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：14位代码</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称
+如果有多个选项，使用&amp;分隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称
+如果有多个选项，使用&amp;分隔</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称
+选项：单位，个人，个人及单位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称
+如果有多个选项，使用&amp;分隔      选项：广义政府&amp;非金融性公司&amp;金融性公司&amp;住户部门&amp;国外部门</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称
+如果有多个选项，使用&amp;分隔      选项：内部增级&amp;外部增级</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：主动管理业务、被动管理业务</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：独立运作、银信合作、银保合作、银基合作、银证合作、混合类、其他、不适用</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：是、否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：商业银行发行、理财子公司发行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>产品基本信息:</t>
@@ -3026,22 +3136,6 @@
   </si>
   <si>
     <t>${data.lowYieldIssueToString}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宁夏回族自治区</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>发起机构代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发起机构名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${data.issuePartyName}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3089,6 +3183,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -3142,13 +3241,6 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3158,9 +3250,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -3224,20 +3334,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3255,46 +3377,46 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -3303,37 +3425,34 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3637,242 +3756,349 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL2"/>
-  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AK3"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="15.6640625" style="5"/>
+    <col min="1" max="16384" width="15.625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="2" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>734</v>
+    <row r="1" spans="1:37" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="C1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" s="6" customFormat="1" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="S2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="T2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="U2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="V2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="Z2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AB2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AC2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK2" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="A3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AF1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>736</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG2" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="AH2" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI2" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="AJ2" s="5" t="s">
+      <c r="H3" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="AK2" s="5" t="s">
+      <c r="I3" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="AL2" s="5" t="s">
+      <c r="J3" s="9" t="s">
         <v>154</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB3" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AC3" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD3" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE3" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="AF3" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="AG3" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="AK3" s="9" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3885,2254 +4111,2260 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="14.625" style="5" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="27" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A1" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27" t="s">
+      <c r="B1" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27" t="s">
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27" t="s">
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27" t="s">
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27" t="s">
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="28" t="s">
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A2" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A3" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A4" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A5" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A7" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A11" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A12" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A13" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A14" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A15" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A16" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A17" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A18" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A19" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A20" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A21" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A22" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="R22" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="R23" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A24" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A25" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A26" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="P26" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q26" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="R26" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A27" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q27" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="R27" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A28" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="R28" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="S28" s="9" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A29" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A30" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="R30" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="S30" s="9" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A31" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q31" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="R31" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="S31" s="9" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A32" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="P32" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q32" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="R32" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="S32" s="9" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A33" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="P33" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="R33" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="S33" s="9" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A34" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="P34" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="R34" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="S34" s="9" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A35" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="L2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="O2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="R2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>544</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>545</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="B35" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="E35" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="H35" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="O7" s="5" t="s">
+      <c r="K35" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="M35" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="P7" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="R7" s="5" t="s">
+      <c r="N35" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="P35" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="S7" s="5" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="Q35" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="R35" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="S35" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="5" t="s">
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A36" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="I8" s="5" t="s">
+      <c r="E36" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G36" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="H36" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="O8" s="5" t="s">
+      <c r="K36" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="M36" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="P8" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="R8" s="5" t="s">
+      <c r="N36" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="P36" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="Q36" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="R36" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="S36" s="9" t="s">
         <v>563</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="S13" s="5" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="P15" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="S15" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="R17" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="P18" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="R18" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>624</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="P19" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="R19" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="P20" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="R20" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="S20" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="N21" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="P21" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q21" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="R21" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="S21" s="5" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>641</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="R22" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="S22" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>650</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="S23" s="5" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="P24" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q24" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="R24" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="S24" s="5" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="O25" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="P25" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q25" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="R25" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="S25" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>667</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>668</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>669</v>
-      </c>
-      <c r="P26" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="R26" s="5" t="s">
-        <v>670</v>
-      </c>
-      <c r="S26" s="5" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>672</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>673</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="N27" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>675</v>
-      </c>
-      <c r="P27" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q27" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="R27" s="5" t="s">
-        <v>676</v>
-      </c>
-      <c r="S27" s="5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>678</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>679</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>680</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>681</v>
-      </c>
-      <c r="P28" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q28" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="R28" s="5" t="s">
-        <v>682</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>683</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>684</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>685</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>686</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="O29" s="5" t="s">
-        <v>687</v>
-      </c>
-      <c r="P29" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q29" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="R29" s="5" t="s">
-        <v>688</v>
-      </c>
-      <c r="S29" s="5" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>689</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>691</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="N30" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="O30" s="5" t="s">
-        <v>693</v>
-      </c>
-      <c r="P30" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="Q30" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="R30" s="5" t="s">
-        <v>694</v>
-      </c>
-      <c r="S30" s="5" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>697</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="N31" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="O31" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="P31" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q31" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="R31" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="S31" s="5" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>701</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>702</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>703</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="N32" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="O32" s="5" t="s">
-        <v>705</v>
-      </c>
-      <c r="P32" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q32" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="R32" s="5" t="s">
-        <v>706</v>
-      </c>
-      <c r="S32" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>707</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="N33" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="O33" s="5" t="s">
-        <v>711</v>
-      </c>
-      <c r="P33" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q33" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="R33" s="5" t="s">
-        <v>712</v>
-      </c>
-      <c r="S33" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>715</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="N34" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="O34" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="P34" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="R34" s="5" t="s">
-        <v>718</v>
-      </c>
-      <c r="S34" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
-        <v>733</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>719</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>720</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>721</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>722</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="N35" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="O35" s="5" t="s">
-        <v>723</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="R35" s="5" t="s">
-        <v>724</v>
-      </c>
-      <c r="S35" s="5" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>725</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>727</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>728</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="N36" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="O36" s="5" t="s">
-        <v>729</v>
-      </c>
-      <c r="P36" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="R36" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="S36" s="5" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="9"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="B1:D1"/>
@@ -6140,237 +6372,230 @@
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="75.88671875" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="46.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="75.875" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="15"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="15"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19"/>
-      <c r="B15" s="17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="17" t="s">
+    <row r="1" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
+    <row r="3" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="17" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="17" t="s">
+      <c r="D4" s="19"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="D5" s="19"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+    <row r="7" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="31"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="B7" s="21" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
+    <row r="8" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="32" t="s">
+      <c r="B8" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="B26" s="31"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="31"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="20"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="24"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
+      <c r="B10" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="24"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="34"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="21"/>
-      <c r="B34" s="25"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
+      <c r="B11" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="B35" s="36"/>
+    </row>
+    <row r="12" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
+      <c r="B15" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="23"/>
+      <c r="B16" s="21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="23"/>
+      <c r="B20" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A21" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A22" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="34"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A24" s="25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A25" s="26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A26" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="34"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A27" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="34"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A28" s="24"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A31" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="28"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A32" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="28"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A33" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="37"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A34" s="25"/>
+      <c r="B34" s="29"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A35" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6380,7 +6605,7 @@
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A35:B35"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ZGBS-CP\feature-3.0.4\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="600" yWindow="135" windowWidth="19395" windowHeight="7065"/>
   </bookViews>
@@ -133,9 +138,6 @@
     <t>${data.prodBrand}</t>
   </si>
   <si>
-    <t>${data.prodStage}</t>
-  </si>
-  <si>
     <t>${data.raiseType}</t>
   </si>
   <si>
@@ -3136,6 +3138,10 @@
   </si>
   <si>
     <t>${data.lowYieldIssueToString}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${data.prodStageToString}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3425,14 +3431,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -3465,12 +3471,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3512,7 +3521,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3547,7 +3556,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3764,115 +3773,115 @@
   <sheetData>
     <row r="1" spans="1:37" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="Q1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK1" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="6" customFormat="1" ht="28.5" x14ac:dyDescent="0.15">
@@ -3964,10 +3973,10 @@
         <v>28</v>
       </c>
       <c r="AD2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE2" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="AF2" s="6" t="s">
         <v>29</v>
@@ -3996,109 +4005,109 @@
         <v>36</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="P3" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="N3" s="9" t="s">
-        <v>756</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>757</v>
-      </c>
-      <c r="P3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="S3" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="W3" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="X3" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="Y3" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="Z3" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="AA3" s="9" t="s">
+      <c r="AB3" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AC3" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="AC3" s="9" t="s">
+      <c r="AD3" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="AD3" s="9" t="s">
+      <c r="AE3" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AE3" s="9" t="s">
+      <c r="AF3" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="AF3" s="9" t="s">
+      <c r="AG3" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="AG3" s="9" t="s">
+      <c r="AH3" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="AH3" s="9" t="s">
+      <c r="AI3" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="AI3" s="9" t="s">
+      <c r="AJ3" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="AJ3" s="9" t="s">
+      <c r="AK3" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="AK3" s="9" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4118,2103 +4127,2103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32" t="s">
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32" t="s">
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32" t="s">
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32" t="s">
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32" t="s">
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A3" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A2" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" s="31" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A3" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="G3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" s="10" t="s">
+      <c r="K3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="M3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="10" t="s">
+      <c r="N3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="P3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P3" s="10" t="s">
+      <c r="Q3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="S3" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A4" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="J4" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="L4" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="N4" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="O4" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="P4" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="Q4" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="R4" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="S4" s="9" t="s">
         <v>376</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="L5" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="O5" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="P5" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="Q5" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="R5" s="12" t="s">
         <v>568</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="S5" s="12" t="s">
         <v>376</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="S5" s="12" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A6" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="F6" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="L6" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="M6" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="N6" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="P6" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="Q6" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="R6" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="S6" s="9" t="s">
         <v>382</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A7" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="I7" s="12" t="s">
         <v>577</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="K7" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="L7" s="9" t="s">
         <v>578</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="M7" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="N7" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="O7" s="9" t="s">
         <v>579</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="P7" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="Q7" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="R7" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="S7" s="9" t="s">
         <v>388</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A8" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="I8" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="J8" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="K8" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="L8" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="S8" s="9" t="s">
         <v>394</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A9" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="J9" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="K9" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="L9" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="M9" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="P9" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="Q9" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="R9" s="9" t="s">
         <v>592</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="S9" s="9" t="s">
         <v>400</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A10" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>595</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="J10" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="K10" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="L10" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="O10" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="P10" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="Q10" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="R10" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="S10" s="9" t="s">
         <v>406</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>599</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="I11" s="9" t="s">
         <v>601</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="J11" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="K11" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="L11" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="M11" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="N11" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="O11" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="P11" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="Q11" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="R11" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="S11" s="9" t="s">
         <v>412</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A12" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>606</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="I12" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="J12" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="K12" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="L12" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="M12" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="N12" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="O12" s="9" t="s">
         <v>609</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="P12" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="Q12" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="R12" s="9" t="s">
         <v>610</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="S12" s="9" t="s">
         <v>418</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A13" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>612</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="I13" s="9" t="s">
         <v>613</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="J13" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="K13" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="L13" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="M13" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="O13" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="P13" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="Q13" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="R13" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="P13" s="9" t="s">
+      <c r="S13" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A14" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>618</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="I14" s="9" t="s">
         <v>619</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="J14" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="K14" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="L14" s="9" t="s">
         <v>620</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="M14" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="N14" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="O14" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="P14" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="Q14" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="O14" s="9" t="s">
+      <c r="R14" s="9" t="s">
         <v>622</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="S14" s="9" t="s">
         <v>430</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="S14" s="9" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="I15" s="9" t="s">
         <v>625</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="J15" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="K15" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="L15" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="M15" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="N15" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="O15" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="P15" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="Q15" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="O15" s="9" t="s">
+      <c r="R15" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="P15" s="9" t="s">
+      <c r="S15" s="9" t="s">
         <v>436</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A16" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="F16" s="9" t="s">
         <v>630</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="G16" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="I16" s="9" t="s">
         <v>631</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="J16" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="K16" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="L16" s="9" t="s">
         <v>632</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="M16" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="N16" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="O16" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="P16" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="Q16" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="O16" s="9" t="s">
+      <c r="R16" s="9" t="s">
         <v>634</v>
       </c>
-      <c r="P16" s="9" t="s">
+      <c r="S16" s="9" t="s">
         <v>442</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="R16" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A17" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="I17" s="9" t="s">
         <v>637</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="J17" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="K17" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="L17" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="M17" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="N17" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="O17" s="9" t="s">
         <v>639</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="P17" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="Q17" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="O17" s="9" t="s">
+      <c r="R17" s="9" t="s">
         <v>640</v>
       </c>
-      <c r="P17" s="9" t="s">
+      <c r="S17" s="9" t="s">
         <v>448</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="S17" s="9" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A18" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="F18" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="I18" s="9" t="s">
         <v>643</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="J18" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="K18" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="L18" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="M18" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="N18" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="O18" s="9" t="s">
         <v>645</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="P18" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="Q18" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="O18" s="9" t="s">
+      <c r="R18" s="9" t="s">
         <v>646</v>
       </c>
-      <c r="P18" s="9" t="s">
+      <c r="S18" s="9" t="s">
         <v>454</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A19" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="I19" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="J19" s="9" t="s">
         <v>457</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="K19" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="L19" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="M19" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="N19" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="O19" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="P19" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="Q19" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="O19" s="9" t="s">
+      <c r="R19" s="9" t="s">
         <v>652</v>
       </c>
-      <c r="P19" s="9" t="s">
+      <c r="S19" s="9" t="s">
         <v>460</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="R19" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="S19" s="9" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A20" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="F20" s="9" t="s">
         <v>654</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="H20" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="I20" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="J20" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="K20" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="L20" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="M20" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="N20" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="O20" s="9" t="s">
         <v>657</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="P20" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="Q20" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="O20" s="9" t="s">
+      <c r="R20" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="P20" s="9" t="s">
+      <c r="S20" s="9" t="s">
         <v>466</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="R20" s="9" t="s">
-        <v>659</v>
-      </c>
-      <c r="S20" s="9" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A21" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="H21" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="I21" s="9" t="s">
         <v>661</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="J21" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="K21" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="L21" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="M21" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="N21" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="O21" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="P21" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="Q21" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="O21" s="9" t="s">
+      <c r="R21" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="P21" s="9" t="s">
+      <c r="S21" s="9" t="s">
         <v>472</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="R21" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="S21" s="9" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A22" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>666</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="G22" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="H22" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="I22" s="9" t="s">
         <v>667</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="J22" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="K22" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="L22" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="M22" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="N22" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="O22" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="P22" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="Q22" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="O22" s="9" t="s">
+      <c r="R22" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="P22" s="9" t="s">
+      <c r="S22" s="9" t="s">
         <v>478</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="R22" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="S22" s="9" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="F23" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="G23" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="I23" s="9" t="s">
         <v>673</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="J23" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="K23" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="L23" s="9" t="s">
         <v>674</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="M23" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="N23" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="O23" s="9" t="s">
         <v>675</v>
       </c>
-      <c r="M23" s="9" t="s">
+      <c r="P23" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="N23" s="9" t="s">
+      <c r="Q23" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="O23" s="9" t="s">
+      <c r="R23" s="9" t="s">
         <v>676</v>
       </c>
-      <c r="P23" s="9" t="s">
+      <c r="S23" s="9" t="s">
         <v>484</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="R23" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="S23" s="9" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A24" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="G24" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="H24" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="I24" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="J24" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="K24" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="L24" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="M24" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="N24" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="O24" s="9" t="s">
         <v>681</v>
       </c>
-      <c r="M24" s="9" t="s">
+      <c r="P24" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="Q24" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="O24" s="9" t="s">
+      <c r="R24" s="9" t="s">
         <v>682</v>
       </c>
-      <c r="P24" s="9" t="s">
+      <c r="S24" s="9" t="s">
         <v>490</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="R24" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="S24" s="9" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A25" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="G25" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="H25" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="I25" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="J25" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="K25" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="L25" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="M25" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="K25" s="9" t="s">
+      <c r="N25" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="O25" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="M25" s="9" t="s">
+      <c r="P25" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="Q25" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="O25" s="9" t="s">
+      <c r="R25" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="P25" s="9" t="s">
+      <c r="S25" s="9" t="s">
         <v>496</v>
-      </c>
-      <c r="Q25" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="R25" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="S25" s="9" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A26" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="F26" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="G26" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="H26" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="I26" s="9" t="s">
         <v>691</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="J26" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="K26" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="L26" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="M26" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="N26" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="O26" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="M26" s="9" t="s">
+      <c r="P26" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="Q26" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="O26" s="9" t="s">
+      <c r="R26" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="P26" s="9" t="s">
+      <c r="S26" s="9" t="s">
         <v>502</v>
-      </c>
-      <c r="Q26" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="R26" s="9" t="s">
-        <v>695</v>
-      </c>
-      <c r="S26" s="9" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A27" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B27" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>696</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="G27" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="H27" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="I27" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="J27" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="K27" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="L27" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="M27" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="K27" s="9" t="s">
+      <c r="N27" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="O27" s="9" t="s">
         <v>699</v>
       </c>
-      <c r="M27" s="9" t="s">
+      <c r="P27" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="Q27" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="O27" s="9" t="s">
+      <c r="R27" s="9" t="s">
         <v>700</v>
       </c>
-      <c r="P27" s="9" t="s">
+      <c r="S27" s="9" t="s">
         <v>508</v>
-      </c>
-      <c r="Q27" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="R27" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="S27" s="9" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A28" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="F28" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="G28" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="H28" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="I28" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="J28" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="K28" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="L28" s="9" t="s">
         <v>704</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="M28" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="N28" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="O28" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="M28" s="9" t="s">
+      <c r="P28" s="9" t="s">
         <v>513</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="Q28" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="O28" s="9" t="s">
+      <c r="R28" s="9" t="s">
         <v>706</v>
       </c>
-      <c r="P28" s="9" t="s">
+      <c r="S28" s="9" t="s">
         <v>514</v>
-      </c>
-      <c r="Q28" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="R28" s="9" t="s">
-        <v>707</v>
-      </c>
-      <c r="S28" s="9" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B29" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="F29" s="9" t="s">
         <v>708</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="G29" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="H29" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="I29" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="J29" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="K29" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="L29" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="M29" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="K29" s="9" t="s">
+      <c r="N29" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="L29" s="9" t="s">
+      <c r="O29" s="9" t="s">
         <v>711</v>
       </c>
-      <c r="M29" s="9" t="s">
+      <c r="P29" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="Q29" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="O29" s="9" t="s">
+      <c r="R29" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="P29" s="9" t="s">
+      <c r="S29" s="9" t="s">
         <v>520</v>
-      </c>
-      <c r="Q29" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="R29" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="S29" s="9" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A30" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="F30" s="9" t="s">
         <v>714</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="G30" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="H30" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="I30" s="9" t="s">
         <v>715</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="J30" s="9" t="s">
         <v>523</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="K30" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="L30" s="9" t="s">
         <v>716</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="M30" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="K30" s="9" t="s">
+      <c r="N30" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="O30" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="M30" s="9" t="s">
+      <c r="P30" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="N30" s="9" t="s">
+      <c r="Q30" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="O30" s="9" t="s">
+      <c r="R30" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="P30" s="9" t="s">
+      <c r="S30" s="9" t="s">
         <v>526</v>
-      </c>
-      <c r="Q30" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="R30" s="9" t="s">
-        <v>719</v>
-      </c>
-      <c r="S30" s="9" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A31" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B31" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="F31" s="9" t="s">
         <v>720</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="G31" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="H31" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="I31" s="9" t="s">
         <v>721</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="J31" s="9" t="s">
         <v>529</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="K31" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="L31" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="M31" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="K31" s="9" t="s">
+      <c r="N31" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="O31" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="M31" s="9" t="s">
+      <c r="P31" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="Q31" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="O31" s="9" t="s">
+      <c r="R31" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="P31" s="9" t="s">
+      <c r="S31" s="9" t="s">
         <v>532</v>
-      </c>
-      <c r="Q31" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="R31" s="9" t="s">
-        <v>725</v>
-      </c>
-      <c r="S31" s="9" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A32" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B32" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="F32" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="G32" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="H32" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="I32" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="J32" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="K32" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="L32" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="M32" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="K32" s="9" t="s">
+      <c r="N32" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="O32" s="9" t="s">
         <v>729</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="P32" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="N32" s="9" t="s">
+      <c r="Q32" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="O32" s="9" t="s">
+      <c r="R32" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="P32" s="9" t="s">
+      <c r="S32" s="9" t="s">
         <v>538</v>
-      </c>
-      <c r="Q32" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="R32" s="9" t="s">
-        <v>731</v>
-      </c>
-      <c r="S32" s="9" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A33" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B33" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="F33" s="9" t="s">
         <v>732</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="G33" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="I33" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="J33" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="K33" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="L33" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="M33" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="K33" s="9" t="s">
+      <c r="N33" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="O33" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="M33" s="9" t="s">
+      <c r="P33" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="N33" s="9" t="s">
+      <c r="Q33" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="O33" s="9" t="s">
+      <c r="R33" s="9" t="s">
         <v>736</v>
       </c>
-      <c r="P33" s="9" t="s">
+      <c r="S33" s="9" t="s">
         <v>544</v>
-      </c>
-      <c r="Q33" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="R33" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="S33" s="9" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A34" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B34" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="F34" s="9" t="s">
         <v>738</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="G34" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="H34" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="I34" s="9" t="s">
         <v>739</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="J34" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="K34" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="I34" s="9" t="s">
+      <c r="L34" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="J34" s="9" t="s">
+      <c r="M34" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="K34" s="9" t="s">
+      <c r="N34" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="L34" s="9" t="s">
+      <c r="O34" s="9" t="s">
         <v>741</v>
       </c>
-      <c r="M34" s="9" t="s">
+      <c r="P34" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="N34" s="9" t="s">
+      <c r="Q34" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="O34" s="9" t="s">
+      <c r="R34" s="9" t="s">
         <v>742</v>
       </c>
-      <c r="P34" s="9" t="s">
+      <c r="S34" s="9" t="s">
         <v>550</v>
-      </c>
-      <c r="Q34" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="R34" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="S34" s="9" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A35" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B35" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="F35" s="9" t="s">
         <v>744</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="G35" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="H35" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="I35" s="9" t="s">
         <v>745</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="J35" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="K35" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="L35" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="M35" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="K35" s="9" t="s">
+      <c r="N35" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="O35" s="9" t="s">
         <v>747</v>
       </c>
-      <c r="M35" s="9" t="s">
+      <c r="P35" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="Q35" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="O35" s="9" t="s">
+      <c r="R35" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="P35" s="9" t="s">
+      <c r="S35" s="9" t="s">
         <v>556</v>
-      </c>
-      <c r="Q35" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="R35" s="9" t="s">
-        <v>749</v>
-      </c>
-      <c r="S35" s="9" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A36" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="F36" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="G36" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="H36" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="I36" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="J36" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="K36" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="L36" s="9" t="s">
         <v>752</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="M36" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="K36" s="9" t="s">
+      <c r="N36" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="O36" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="M36" s="9" t="s">
+      <c r="P36" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="N36" s="9" t="s">
+      <c r="Q36" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="O36" s="9" t="s">
+      <c r="R36" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="P36" s="9" t="s">
+      <c r="S36" s="9" t="s">
         <v>562</v>
-      </c>
-      <c r="Q36" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="R36" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="S36" s="9" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.15">
@@ -6359,12 +6368,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="B1:D1"/>
@@ -6372,6 +6375,12 @@
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6390,179 +6399,179 @@
   <sheetData>
     <row r="1" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>110</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" s="19"/>
     </row>
     <row r="5" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5" s="19"/>
     </row>
     <row r="6" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>116</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>118</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>121</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>123</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>125</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>127</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="21" t="s">
         <v>129</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="23"/>
       <c r="B15" s="21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="23"/>
       <c r="B16" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>133</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>135</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>137</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="23"/>
       <c r="B20" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B22" s="34"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B26" s="34"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B27" s="34"/>
     </row>
@@ -6571,19 +6580,19 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B31" s="28"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B32" s="28"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B33" s="37"/>
     </row>
@@ -6593,7 +6602,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" s="38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B35" s="39"/>
     </row>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ZGBS-CP\feature-3.0.4\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\ZGBS-CP\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84704E7-F137-47F2-AE10-1456C34E341D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="135" windowWidth="19395" windowHeight="7065"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="765">
   <si>
     <t>发起机构代码</t>
   </si>
@@ -136,6 +137,9 @@
   </si>
   <si>
     <t>${data.prodBrand}</t>
+  </si>
+  <si>
+    <t>${data.prodStage}</t>
   </si>
   <si>
     <t>${data.raiseType}</t>
@@ -436,6 +440,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>资金信托计划</t>
@@ -471,6 +476,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>是</t>
@@ -492,6 +498,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品增信机构类型，产品增信形式</t>
@@ -508,6 +515,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必填</t>
@@ -529,6 +537,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>否</t>
@@ -550,6 +559,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品增信机构类型，产品增信形式</t>
@@ -566,6 +576,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必须为空</t>
@@ -587,6 +598,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>表外</t>
@@ -608,6 +620,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品对应的资产池代码</t>
@@ -624,6 +637,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必填</t>
@@ -645,6 +659,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>非表外</t>
@@ -666,6 +681,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品对应的资产池代码</t>
@@ -682,6 +698,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必须为空</t>
@@ -709,6 +726,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>募集起始日期</t>
@@ -730,6 +748,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>募集结束日期</t>
@@ -754,6 +773,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品起始日期</t>
@@ -778,6 +798,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>预计客户最低年收益率</t>
@@ -800,6 +821,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>币种需要使用中文名称</t>
@@ -816,6 +838,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>多币种间用</t>
@@ -832,6 +855,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>分割。</t>
@@ -845,6 +869,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>收益率需要直接提供</t>
@@ -861,6 +886,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>前数值，例如</t>
@@ -877,6 +903,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>，那么直接提供</t>
@@ -893,6 +920,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>不要带</t>
@@ -909,6 +937,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>，如果带</t>
@@ -925,6 +954,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>号数据会缩小</t>
@@ -941,6 +971,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>倍。</t>
@@ -954,6 +985,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：</t>
@@ -975,6 +1007,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>个币种的人民币合计必填。</t>
@@ -996,6 +1029,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>各省的和；人民币合计</t>
@@ -1012,6 +1046,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>人民币金额</t>
@@ -1028,6 +1063,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>外币的转人民币金额</t>
@@ -1064,6 +1100,7 @@
         <b/>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>导入文件（产品基本信息）的命名规则：</t>
@@ -1077,6 +1114,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：</t>
@@ -1093,6 +1131,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“</t>
@@ -1109,6 +1148,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>”</t>
@@ -1130,6 +1170,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：</t>
@@ -1146,6 +1187,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>文件命名规则：</t>
@@ -1162,6 +1204,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“</t>
@@ -1178,6 +1221,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>”每个</t>
@@ -1194,6 +1238,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>只包含单一产品信息，压缩文件中的文件为</t>
@@ -1210,6 +1255,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>格式，</t>
@@ -1226,6 +1272,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>文件名中不能包含中文字符。</t>
@@ -1247,6 +1294,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单元格样式为文本处理的，如果不是文本</t>
@@ -1263,6 +1311,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>系统会报错。请在录入数据前将</t>
@@ -1279,6 +1328,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单元格样式设置好后再录入数据。</t>
@@ -3141,15 +3191,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>${data.prodStageToString}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>是否现金管理类</t>
+  </si>
+  <si>
+    <t>跨境理财通标识</t>
+  </si>
+  <si>
+    <t>${data.cashManaCate}</t>
+  </si>
+  <si>
+    <t>${data.crossBorderFlag}</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：是、否</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>以财产权信托名义开展的资金信托标识</t>
+  </si>
+  <si>
+    <t>${data.zjxtFlag}</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="17" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3160,28 +3230,33 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3193,22 +3268,26 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3225,6 +3304,7 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3237,6 +3317,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3244,6 +3325,12 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3340,7 +3427,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3431,14 +3518,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -3461,6 +3548,9 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3479,7 +3569,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3554,6 +3644,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -3589,6 +3696,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3764,127 +3888,136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK3"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AN3"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="15.625" style="9"/>
+    <col min="1" max="16384" width="15.6640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:40" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="AK1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="R1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37" s="6" customFormat="1" ht="28.5" x14ac:dyDescent="0.15">
+      <c r="AN1" s="40" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" s="6" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -3973,10 +4106,10 @@
         <v>28</v>
       </c>
       <c r="AD2" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AF2" s="6" t="s">
         <v>29</v>
@@ -3996,8 +4129,17 @@
       <c r="AK2" s="8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AL2" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="AM2" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="AN2" s="6" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>35</v>
       </c>
@@ -4005,109 +4147,118 @@
         <v>36</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="O3" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>756</v>
-      </c>
       <c r="P3" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="X3" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD3" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AE3" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AF3" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG3" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AH3" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AI3" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ3" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AK3" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="AM3" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="AN3" s="9" t="s">
+        <v>764</v>
       </c>
     </row>
   </sheetData>
@@ -4118,2115 +4269,2115 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S43"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="5" customWidth="1"/>
     <col min="2" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A1" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="30" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30" t="s">
+      <c r="B1" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30" t="s">
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30" t="s">
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30" t="s">
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30" t="s">
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
-        <v>41</v>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="B2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="R22" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="R23" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="P26" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q26" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="R26" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q27" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="R27" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="R28" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="S28" s="9" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="R30" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="S30" s="9" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q31" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="R31" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="S31" s="9" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="P32" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q32" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="R32" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="S32" s="9" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="P33" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="R33" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="S33" s="9" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="P34" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="R34" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="S34" s="9" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q35" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="R35" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="S35" s="9" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="O2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="R2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A3" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A4" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B36" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="P36" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q36" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="R36" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="S36" s="9" t="s">
         <v>563</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>567</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>568</v>
-      </c>
-      <c r="S5" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A6" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A7" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>577</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>579</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>580</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>584</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>590</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>591</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A10" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>595</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>599</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A12" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A13" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A14" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="S14" s="9" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A15" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A16" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="R16" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A17" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="S17" s="9" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A18" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>646</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A19" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="R19" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="S19" s="9" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A20" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="R20" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="S20" s="9" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A21" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>659</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>661</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="R21" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="S21" s="9" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A22" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="R22" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="S22" s="9" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A23" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="R23" s="9" t="s">
-        <v>676</v>
-      </c>
-      <c r="S23" s="9" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A24" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="R24" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="S24" s="9" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A25" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>686</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q25" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="R25" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="S25" s="9" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A26" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="Q26" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="R26" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="S26" s="9" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A27" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>695</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>696</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>697</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>698</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>699</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q27" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="R27" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="S27" s="9" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A28" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>703</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q28" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="R28" s="9" t="s">
-        <v>706</v>
-      </c>
-      <c r="S28" s="9" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A29" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>707</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>708</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>709</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>710</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>711</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q29" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="R29" s="9" t="s">
-        <v>712</v>
-      </c>
-      <c r="S29" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>715</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>716</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>717</v>
-      </c>
-      <c r="P30" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="Q30" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="R30" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="S30" s="9" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A31" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>719</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>721</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="Q31" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="R31" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="S31" s="9" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A32" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>725</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>726</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="O32" s="9" t="s">
-        <v>729</v>
-      </c>
-      <c r="P32" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q32" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="R32" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="S32" s="9" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A33" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>731</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>733</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q33" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="R33" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="S33" s="9" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A34" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>738</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>739</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="N34" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="O34" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="P34" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="Q34" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="R34" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="S34" s="9" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A35" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>745</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>746</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q35" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="R35" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="S35" s="9" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A36" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>749</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="L36" s="9" t="s">
-        <v>752</v>
-      </c>
-      <c r="M36" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="N36" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="P36" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="Q36" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="R36" s="9" t="s">
-        <v>754</v>
-      </c>
-      <c r="S36" s="9" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.15">
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -6246,7 +6397,7 @@
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -6266,7 +6417,7 @@
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -6286,7 +6437,7 @@
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -6306,7 +6457,7 @@
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -6326,7 +6477,7 @@
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -6346,7 +6497,7 @@
       <c r="R42" s="9"/>
       <c r="S42" s="9"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -6368,6 +6519,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="B1:D1"/>
@@ -6375,12 +6532,6 @@
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6388,221 +6539,221 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="75.875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="46.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="75.88671875" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D4" s="19"/>
     </row>
-    <row r="5" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D5" s="19"/>
     </row>
-    <row r="6" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B8" s="21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
-        <v>117</v>
-      </c>
       <c r="B9" s="21" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23"/>
       <c r="B15" s="21" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23"/>
       <c r="B16" s="21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23"/>
       <c r="B20" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B22" s="34"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B26" s="34"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B27" s="34"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B31" s="28"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B32" s="28"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B33" s="37"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="25"/>
       <c r="B34" s="29"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B35" s="39"/>
     </row>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\ZGBS-CP\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ZGBS-CP\feature-3.0.4\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84704E7-F137-47F2-AE10-1456C34E341D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -139,9 +138,6 @@
     <t>${data.prodBrand}</t>
   </si>
   <si>
-    <t>${data.prodStage}</t>
-  </si>
-  <si>
     <t>${data.raiseType}</t>
   </si>
   <si>
@@ -3214,11 +3210,15 @@
     <t>${data.zjxtFlag}</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
+  <si>
+    <t>${data.prodStageToString}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3518,6 +3518,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -3548,9 +3551,6 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3569,7 +3569,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3644,23 +3644,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -3696,23 +3679,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3888,136 +3854,136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AN3"/>
-  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="15.6640625" style="9"/>
+    <col min="1" max="16384" width="15.625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="Q1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AJ1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="AL1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AN1" s="40" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="2" spans="1:40" s="6" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="AN1" s="30" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" s="6" customFormat="1" ht="42.75" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -4106,10 +4072,10 @@
         <v>28</v>
       </c>
       <c r="AD2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE2" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="AF2" s="6" t="s">
         <v>29</v>
@@ -4130,16 +4096,16 @@
         <v>34</v>
       </c>
       <c r="AL2" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="AM2" s="6" t="s">
         <v>758</v>
       </c>
-      <c r="AM2" s="6" t="s">
-        <v>759</v>
-      </c>
       <c r="AN2" s="6" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
         <v>35</v>
       </c>
@@ -4147,118 +4113,118 @@
         <v>36</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="P3" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="N3" s="9" t="s">
-        <v>756</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>757</v>
-      </c>
-      <c r="P3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="S3" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="W3" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="X3" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="Y3" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="Z3" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="AA3" s="9" t="s">
+      <c r="AB3" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AC3" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="AC3" s="9" t="s">
+      <c r="AD3" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="AD3" s="9" t="s">
+      <c r="AE3" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AE3" s="9" t="s">
+      <c r="AF3" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="AF3" s="9" t="s">
+      <c r="AG3" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="AG3" s="9" t="s">
+      <c r="AH3" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="AH3" s="9" t="s">
+      <c r="AI3" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="AI3" s="9" t="s">
+      <c r="AJ3" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="AJ3" s="9" t="s">
+      <c r="AK3" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="AK3" s="9" t="s">
-        <v>179</v>
-      </c>
       <c r="AL3" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="AM3" s="9" t="s">
         <v>760</v>
       </c>
-      <c r="AM3" s="9" t="s">
-        <v>761</v>
-      </c>
       <c r="AN3" s="9" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
   </sheetData>
@@ -4269,2115 +4235,2115 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="14.625" style="5" customWidth="1"/>
     <col min="2" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A1" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32" t="s">
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32" t="s">
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32" t="s">
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A3" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" s="31" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="E3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="B4" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A5" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B5" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="L5" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="O5" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="P5" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="Q5" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="R5" s="12" t="s">
         <v>568</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="S5" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="Q4" s="9" t="s">
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="C6" s="12" t="s">
         <v>569</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="S5" s="12" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="E6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A7" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q6" s="9" t="s">
+      <c r="B7" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="R6" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="E7" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>578</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>579</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>580</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q7" s="9" t="s">
+      <c r="B8" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="R7" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="E8" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A9" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>584</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q8" s="9" t="s">
+      <c r="B9" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="E9" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>590</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>591</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q9" s="9" t="s">
+      <c r="B10" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="R9" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="S9" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="E10" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A11" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>595</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q10" s="9" t="s">
+      <c r="B11" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="R10" s="9" t="s">
+      <c r="C11" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="E11" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A12" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="Q11" s="9" t="s">
+      <c r="B12" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="R11" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="S11" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="E12" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A13" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q12" s="9" t="s">
+      <c r="B13" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="R12" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>611</v>
       </c>
-      <c r="S12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="E13" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A14" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="Q13" s="9" t="s">
+      <c r="B14" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="R13" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="E14" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A15" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q14" s="9" t="s">
+      <c r="B15" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="R14" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="S14" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="E15" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A16" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="Q15" s="9" t="s">
+      <c r="B16" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="R15" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="S15" s="9" t="s">
+      <c r="D16" s="9" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="E16" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A17" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="Q16" s="9" t="s">
+      <c r="B17" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="R16" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="S16" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="E17" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A18" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="Q17" s="9" t="s">
+      <c r="B18" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="R17" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="S17" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="E18" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A19" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>646</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q18" s="9" t="s">
+      <c r="B19" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="R18" s="9" t="s">
+      <c r="C19" s="9" t="s">
         <v>647</v>
       </c>
-      <c r="S18" s="9" t="s">
+      <c r="D19" s="9" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="E19" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q19" s="9" t="s">
+      <c r="B20" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="R19" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="S19" s="9" t="s">
+      <c r="D20" s="9" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="E20" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A21" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="Q20" s="9" t="s">
+      <c r="B21" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="R20" s="9" t="s">
+      <c r="C21" s="9" t="s">
         <v>659</v>
       </c>
-      <c r="S20" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="E21" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A22" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>661</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q21" s="9" t="s">
+      <c r="B22" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="R21" s="9" t="s">
+      <c r="C22" s="9" t="s">
         <v>665</v>
       </c>
-      <c r="S21" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="E22" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="R22" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="Q22" s="9" t="s">
+      <c r="B23" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="R22" s="9" t="s">
+      <c r="C23" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="S22" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="E23" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="R23" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A24" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>676</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q23" s="9" t="s">
+      <c r="B24" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="R23" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>677</v>
       </c>
-      <c r="S23" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="E24" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q24" s="9" t="s">
+      <c r="B25" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="R24" s="9" t="s">
+      <c r="C25" s="9" t="s">
         <v>683</v>
       </c>
-      <c r="S24" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+      <c r="E25" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A26" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>686</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="Q25" s="9" t="s">
+      <c r="B26" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="R25" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="S25" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="E26" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="P26" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q26" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="R26" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A27" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q26" s="9" t="s">
+      <c r="B27" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="R26" s="9" t="s">
+      <c r="C27" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="S26" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+      <c r="E27" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q27" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="R27" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A28" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>696</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>697</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>698</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>699</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="Q27" s="9" t="s">
+      <c r="B28" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="R27" s="9" t="s">
+      <c r="C28" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="S27" s="9" t="s">
+      <c r="D28" s="9" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+      <c r="E28" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="R28" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="S28" s="9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A29" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>703</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>706</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="Q28" s="9" t="s">
+      <c r="B29" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="R28" s="9" t="s">
+      <c r="C29" s="9" t="s">
         <v>707</v>
       </c>
-      <c r="S28" s="9" t="s">
+      <c r="D29" s="9" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="E29" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A30" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>708</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>709</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>710</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>711</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>712</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q29" s="9" t="s">
+      <c r="B30" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="R29" s="9" t="s">
+      <c r="C30" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="S29" s="9" t="s">
+      <c r="D30" s="9" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+      <c r="E30" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="R30" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="S30" s="9" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A31" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>715</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>716</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>717</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="P30" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q30" s="9" t="s">
+      <c r="B31" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="R30" s="9" t="s">
+      <c r="C31" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="S30" s="9" t="s">
+      <c r="D31" s="9" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+      <c r="E31" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q31" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="R31" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="S31" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A32" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>721</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q31" s="9" t="s">
+      <c r="B32" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="R31" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="S31" s="9" t="s">
+      <c r="D32" s="9" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
+      <c r="E32" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="P32" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q32" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="R32" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="S32" s="9" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A33" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>726</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>729</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="O32" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="P32" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q32" s="9" t="s">
+      <c r="B33" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="R32" s="9" t="s">
+      <c r="C33" s="9" t="s">
         <v>731</v>
       </c>
-      <c r="S32" s="9" t="s">
+      <c r="D33" s="9" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+      <c r="E33" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="P33" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="R33" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="S33" s="9" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A34" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>733</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="Q33" s="9" t="s">
+      <c r="B34" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="R33" s="9" t="s">
+      <c r="C34" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="S33" s="9" t="s">
+      <c r="D34" s="9" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
+      <c r="E34" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="P34" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="R34" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="S34" s="9" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A35" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>738</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>739</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="N34" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="O34" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="P34" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="Q34" s="9" t="s">
+      <c r="B35" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="R34" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="S34" s="9" t="s">
+      <c r="D35" s="9" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
+      <c r="E35" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q35" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="R35" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="S35" s="9" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A36" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>745</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>746</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="Q35" s="9" t="s">
+      <c r="B36" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="R35" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>749</v>
       </c>
-      <c r="S35" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="F36" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="G36" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="H36" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="I36" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="J36" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="K36" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="L36" s="9" t="s">
         <v>752</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="M36" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="K36" s="9" t="s">
+      <c r="N36" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="O36" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="M36" s="9" t="s">
+      <c r="P36" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="N36" s="9" t="s">
+      <c r="Q36" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="O36" s="9" t="s">
+      <c r="R36" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="P36" s="9" t="s">
+      <c r="S36" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="Q36" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="R36" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="S36" s="9" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -6397,7 +6363,7 @@
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -6417,7 +6383,7 @@
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -6437,7 +6403,7 @@
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -6457,7 +6423,7 @@
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -6477,7 +6443,7 @@
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -6497,7 +6463,7 @@
       <c r="R42" s="9"/>
       <c r="S42" s="9"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -6539,223 +6505,223 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="75.88671875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="46.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="75.875" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" s="19"/>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5" s="19"/>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="B7" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="21" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="B8" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="21" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="21" t="s">
+    <row r="10" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="22" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="B11" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="22" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="B12" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="22" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="B13" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="22" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="B14" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="23"/>
       <c r="B15" s="21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="23"/>
       <c r="B16" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
+      <c r="B17" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="B17" s="21" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="21" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+      <c r="B19" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="23"/>
       <c r="B20" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A21" s="24" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A22" s="34" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="33" t="s">
+      <c r="B22" s="35"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A24" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B22" s="34"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A25" s="26" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A26" s="36" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="35" t="s">
+      <c r="B26" s="35"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A27" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="34"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
+      <c r="B27" s="35"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A28" s="24"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A31" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="34"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
+      <c r="B31" s="28"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A32" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="28"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
+      <c r="B32" s="28"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A33" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="B32" s="28"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="B33" s="37"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="38"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="25"/>
       <c r="B34" s="29"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="B35" s="39"/>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A35" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="B35" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ZGBS-CP\feature-3.0.4\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\GZYH\zgbszz-guangzhouyinghang\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC66CC56-F9BB-4486-9BBC-99E65F56C133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -3187,9 +3188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是否现金管理类</t>
-  </si>
-  <si>
     <t>跨境理财通标识</t>
   </si>
   <si>
@@ -3212,13 +3210,17 @@
   </si>
   <si>
     <t>${data.prodStageToString}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现金管理类产品标识</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3521,14 +3523,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -3569,7 +3571,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3644,6 +3646,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -3679,6 +3698,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3854,14 +3890,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AN3"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="15.625" style="9"/>
+    <col min="1" max="16384" width="15.6640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:40" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>85</v>
       </c>
@@ -3980,10 +4016,10 @@
         <v>94</v>
       </c>
       <c r="AN1" s="30" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="2" spans="1:40" s="6" customFormat="1" ht="42.75" x14ac:dyDescent="0.15">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" s="6" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -4096,16 +4132,16 @@
         <v>34</v>
       </c>
       <c r="AL2" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="AM2" s="6" t="s">
         <v>757</v>
       </c>
-      <c r="AM2" s="6" t="s">
-        <v>758</v>
-      </c>
       <c r="AN2" s="6" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.15">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>35</v>
       </c>
@@ -4119,7 +4155,7 @@
         <v>37</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>150</v>
@@ -4218,13 +4254,13 @@
         <v>178</v>
       </c>
       <c r="AL3" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="AM3" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="AM3" s="9" t="s">
-        <v>760</v>
-      </c>
       <c r="AN3" s="9" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
   </sheetData>
@@ -4235,51 +4271,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="5" customWidth="1"/>
     <col min="2" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33" t="s">
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33" t="s">
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33" t="s">
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33" t="s">
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33" t="s">
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A2" s="31" t="s">
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="32" t="s">
@@ -4337,8 +4373,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A3" s="31" t="s">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -4396,7 +4432,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>51</v>
       </c>
@@ -4455,7 +4491,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>52</v>
       </c>
@@ -4514,7 +4550,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>53</v>
       </c>
@@ -4573,7 +4609,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>54</v>
       </c>
@@ -4632,7 +4668,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>55</v>
       </c>
@@ -4691,7 +4727,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>56</v>
       </c>
@@ -4750,7 +4786,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -4809,7 +4845,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>58</v>
       </c>
@@ -4868,7 +4904,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>59</v>
       </c>
@@ -4927,7 +4963,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>60</v>
       </c>
@@ -4986,7 +5022,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>61</v>
       </c>
@@ -5045,7 +5081,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>62</v>
       </c>
@@ -5104,7 +5140,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>63</v>
       </c>
@@ -5163,7 +5199,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>64</v>
       </c>
@@ -5222,7 +5258,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>65</v>
       </c>
@@ -5281,7 +5317,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>66</v>
       </c>
@@ -5340,7 +5376,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>67</v>
       </c>
@@ -5399,7 +5435,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>68</v>
       </c>
@@ -5458,7 +5494,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>69</v>
       </c>
@@ -5517,7 +5553,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>70</v>
       </c>
@@ -5576,7 +5612,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>71</v>
       </c>
@@ -5635,7 +5671,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>72</v>
       </c>
@@ -5694,7 +5730,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>73</v>
       </c>
@@ -5753,7 +5789,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>74</v>
       </c>
@@ -5812,7 +5848,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>75</v>
       </c>
@@ -5871,7 +5907,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>76</v>
       </c>
@@ -5930,7 +5966,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>77</v>
       </c>
@@ -5989,7 +6025,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>78</v>
       </c>
@@ -6048,7 +6084,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>79</v>
       </c>
@@ -6107,7 +6143,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>80</v>
       </c>
@@ -6166,7 +6202,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>81</v>
       </c>
@@ -6225,7 +6261,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>82</v>
       </c>
@@ -6284,7 +6320,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>83</v>
       </c>
@@ -6343,7 +6379,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -6363,7 +6399,7 @@
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -6383,7 +6419,7 @@
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -6403,7 +6439,7 @@
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -6423,7 +6459,7 @@
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -6443,7 +6479,7 @@
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -6463,7 +6499,7 @@
       <c r="R42" s="9"/>
       <c r="S42" s="9"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -6485,12 +6521,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="B1:D1"/>
@@ -6498,6 +6528,12 @@
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6505,21 +6541,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="75.875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="46.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="75.88671875" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>109</v>
       </c>
@@ -6527,33 +6563,33 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
         <v>112</v>
       </c>
       <c r="D4" s="19"/>
     </row>
-    <row r="5" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
         <v>113</v>
       </c>
       <c r="D5" s="19"/>
     </row>
-    <row r="6" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>115</v>
       </c>
@@ -6561,7 +6597,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>117</v>
       </c>
@@ -6569,7 +6605,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>117</v>
       </c>
@@ -6577,7 +6613,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>120</v>
       </c>
@@ -6585,7 +6621,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>122</v>
       </c>
@@ -6593,7 +6629,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>124</v>
       </c>
@@ -6601,7 +6637,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>126</v>
       </c>
@@ -6609,7 +6645,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>128</v>
       </c>
@@ -6617,19 +6653,19 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23"/>
       <c r="B15" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23"/>
       <c r="B16" s="21" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>132</v>
       </c>
@@ -6637,7 +6673,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>134</v>
       </c>
@@ -6645,7 +6681,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>136</v>
       </c>
@@ -6653,71 +6689,71 @@
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23"/>
       <c r="B20" s="21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
         <v>140</v>
       </c>
       <c r="B22" s="35"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="36" t="s">
         <v>143</v>
       </c>
       <c r="B26" s="35"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="36" t="s">
         <v>144</v>
       </c>
       <c r="B27" s="35"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
         <v>145</v>
       </c>
       <c r="B31" s="28"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>146</v>
       </c>
       <c r="B32" s="28"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
         <v>147</v>
       </c>
       <c r="B33" s="38"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="25"/>
       <c r="B34" s="29"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="39" t="s">
         <v>148</v>
       </c>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_Oth.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\GZYH\zgbszz-guangzhouyinghang\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\feature3.0.6\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC66CC56-F9BB-4486-9BBC-99E65F56C133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -75,9 +74,6 @@
     <t>募集结束日期</t>
   </si>
   <si>
-    <t>提前终止权标识</t>
-  </si>
-  <si>
     <t>客户赎回权标识</t>
   </si>
   <si>
@@ -112,9 +108,6 @@
     <t>兑付收益币种</t>
   </si>
   <si>
-    <t>增信形式</t>
-  </si>
-  <si>
     <t>受托职责</t>
   </si>
   <si>
@@ -143,10 +136,6 @@
   </si>
   <si>
     <t>客户类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增信机构类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3216,11 +3205,23 @@
     <t>现金管理类产品标识</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>产品增信机构类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品增信形式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发行机构提前终止权标识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3523,14 +3524,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -3571,7 +3572,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3646,23 +3647,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -3698,23 +3682,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3890,136 +3857,136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AN3"/>
-  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="15.6640625" style="9"/>
+    <col min="1" max="16384" width="15.625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" s="5" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Q1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="R1" s="4" t="s">
+      <c r="AA1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AG1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AH1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="AL1" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AN1" s="30" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="2" spans="1:40" s="6" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" s="6" customFormat="1" ht="42.75" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -4072,195 +4039,195 @@
         <v>16</v>
       </c>
       <c r="R2" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="S2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="T2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="V2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="W2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="X2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Z2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="AA2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AB2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AC2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AD2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="AG2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AH2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AG2" s="6" t="s">
+      <c r="AI2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="AH2" s="7" t="s">
+      <c r="AJ2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="AI2" s="8" t="s">
+      <c r="AK2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AJ2" s="8" t="s">
+      <c r="AL2" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="AM2" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="AN2" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AK2" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AL2" s="6" t="s">
-        <v>764</v>
-      </c>
-      <c r="AM2" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="AN2" s="6" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="C3" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="E3" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="H3" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>763</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="N3" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="P3" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="S3" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB3" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC3" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="AD3" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE3" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF3" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG3" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="AK3" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL3" s="9" t="s">
         <v>755</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="AM3" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="P3" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q3" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="S3" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="V3" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="W3" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="X3" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y3" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="Z3" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB3" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC3" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="AD3" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE3" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="AF3" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="AG3" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="AH3" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="AI3" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="AJ3" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="AK3" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="AL3" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="AM3" s="9" t="s">
+      <c r="AN3" s="9" t="s">
         <v>759</v>
-      </c>
-      <c r="AN3" s="9" t="s">
-        <v>762</v>
       </c>
     </row>
   </sheetData>
@@ -4271,2115 +4238,2115 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="14.625" style="5" customWidth="1"/>
     <col min="2" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A1" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31" t="s">
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31" t="s">
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31" t="s">
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A2" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A3" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31" t="s">
+      <c r="C3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31" t="s">
+      <c r="E3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="L2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="O2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="R2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="G3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A4" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="B4" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A5" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A6" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="B6" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A7" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="B7" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A8" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>567</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>568</v>
-      </c>
-      <c r="S5" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="B8" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A9" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="B9" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A10" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>577</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>579</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>580</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="B10" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A11" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>584</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="B11" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A12" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>590</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>591</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="B12" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A13" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>595</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="B13" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A14" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>599</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="B14" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A15" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="B15" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A16" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="B16" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A17" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="S14" s="9" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="B17" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A18" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="B18" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A19" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="R16" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="B19" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A20" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="S17" s="9" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="B20" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A21" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>646</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="B21" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A22" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="R19" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="S19" s="9" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="B22" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="R22" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="R20" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="S20" s="9" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="B23" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="R23" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A24" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>659</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>661</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="R21" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="S21" s="9" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="B24" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A25" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="R22" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="S22" s="9" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="B25" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A26" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="R23" s="9" t="s">
-        <v>676</v>
-      </c>
-      <c r="S23" s="9" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="B26" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="P26" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q26" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="R26" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A27" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="R24" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="S24" s="9" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+      <c r="B27" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q27" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="R27" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A28" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>686</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q25" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="R25" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="S25" s="9" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="B28" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="R28" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="S28" s="9" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="Q26" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="R26" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="S26" s="9" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+      <c r="B29" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>695</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>696</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>697</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>698</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>699</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q27" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="R27" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="S27" s="9" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+      <c r="B30" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="R30" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="S30" s="9" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A31" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>703</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q28" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="R28" s="9" t="s">
-        <v>706</v>
-      </c>
-      <c r="S28" s="9" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="B31" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q31" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="R31" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="S31" s="9" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A32" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>707</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>708</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>709</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>710</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>711</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q29" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="R29" s="9" t="s">
-        <v>712</v>
-      </c>
-      <c r="S29" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+      <c r="B32" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="P32" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q32" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="R32" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="S32" s="9" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A33" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>715</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>716</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>717</v>
-      </c>
-      <c r="P30" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="Q30" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="R30" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="S30" s="9" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+      <c r="B33" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="P33" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="R33" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="S33" s="9" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A34" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>719</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>721</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="Q31" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="R31" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="S31" s="9" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
+      <c r="B34" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="P34" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="R34" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="S34" s="9" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A35" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>725</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>726</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="O32" s="9" t="s">
-        <v>729</v>
-      </c>
-      <c r="P32" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q32" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="R32" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="S32" s="9" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+      <c r="B35" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="Q35" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="R35" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="S35" s="9" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="A36" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>731</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>733</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q33" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="R33" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="S33" s="9" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>738</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>739</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="N34" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="O34" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="P34" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="Q34" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="R34" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="S34" s="9" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>745</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="K35" s="9" t="s">
+      <c r="B36" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="M35" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="O35" s="9" t="s">
+      <c r="F36" s="9" t="s">
         <v>747</v>
       </c>
-      <c r="P35" s="9" t="s">
+      <c r="G36" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="Q35" s="9" t="s">
+      <c r="H36" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="R35" s="9" t="s">
+      <c r="I36" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="S35" s="9" t="s">
+      <c r="J36" s="9" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="K36" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="L36" s="9" t="s">
         <v>749</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="M36" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="N36" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="O36" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="P36" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="Q36" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="R36" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="S36" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="K36" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="L36" s="9" t="s">
-        <v>752</v>
-      </c>
-      <c r="M36" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="N36" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="P36" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="Q36" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="R36" s="9" t="s">
-        <v>754</v>
-      </c>
-      <c r="S36" s="9" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -6399,7 +6366,7 @@
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -6419,7 +6386,7 @@
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -6439,7 +6406,7 @@
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -6459,7 +6426,7 @@
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -6479,7 +6446,7 @@
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -6499,7 +6466,7 @@
       <c r="R42" s="9"/>
       <c r="S42" s="9"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -6521,6 +6488,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="B1:D1"/>
@@ -6528,12 +6501,6 @@
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6541,221 +6508,221 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="75.88671875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="46.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="75.875" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D4" s="19"/>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D5" s="19"/>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="B8" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="21" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+    <row r="10" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B10" s="22" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="21" t="s">
+    <row r="11" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="B11" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="22" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="B12" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="22" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="B13" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="22" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="B14" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="23"/>
       <c r="B15" s="21" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="23"/>
       <c r="B16" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="21" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+      <c r="B19" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:2" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="23"/>
       <c r="B20" s="21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A21" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A22" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="35"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A24" s="25" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A25" s="26" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A26" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B22" s="35"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+      <c r="B26" s="35"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A27" s="36" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+      <c r="B27" s="35"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A28" s="24"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A31" s="27" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
+      <c r="B31" s="28"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A32" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B26" s="35"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
+      <c r="B32" s="28"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A33" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="35"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="B31" s="28"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" s="28"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="37" t="s">
-        <v>147</v>
-      </c>
       <c r="B33" s="38"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="25"/>
       <c r="B34" s="29"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" s="39" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B35" s="40"/>
     </row>
